--- a/diseases/d017/1985-1989.xlsx
+++ b/diseases/d017/1985-1989.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>12</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>29</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>9</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>17</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>25</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>6</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>17</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>6</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9803,9 +9734,6 @@
       </c>
       <c r="O48" t="n">
         <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>

--- a/diseases/d017/1985-1989.xlsx
+++ b/diseases/d017/1985-1989.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,19 +751,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1988-01</t>
+          <t>1985-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>2899</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>2899</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -907,38 +907,38 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1988-01</t>
+          <t>1985-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>2899</v>
       </c>
       <c r="O3" t="n">
-        <v>12</v>
+        <v>2899</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Meslinger</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1141,19 +1141,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1988-02-01</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1988-02</t>
+          <t>1986-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>15796</v>
       </c>
       <c r="O4" t="n">
-        <v>29</v>
+        <v>15796</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1200,42 +1200,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1988-02-01</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1988-02</t>
+          <t>1986-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>29</v>
+        <v>15796</v>
       </c>
       <c r="O5" t="n">
-        <v>29</v>
+        <v>15796</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Meslinger</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1434,42 +1434,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1988-03-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1988-03</t>
+          <t>1987-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>3065</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>3065</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -1590,42 +1590,42 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1687,38 +1687,38 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1988-03-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1988-03</t>
+          <t>1987-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>3065</v>
       </c>
       <c r="O7" t="n">
-        <v>9</v>
+        <v>3065</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Meslinger</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1824,42 +1824,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1988-04-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1988-04</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>17</v>
+        <v>710</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>710</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -1980,42 +1980,42 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2077,38 +2077,38 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1988-04-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1988-04</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>710</v>
       </c>
       <c r="O9" t="n">
-        <v>17</v>
+        <v>710</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Meslinger</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2168,17 +2168,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2214,42 +2214,42 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2311,19 +2311,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1988-05-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1988-05</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2355,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2467,19 +2472,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1988-05-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1988-05</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2581,7 +2586,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2701,19 +2711,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1988-06-01</t>
+          <t>1988-02-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1988-06</t>
+          <t>1988-02</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2737,7 +2747,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2857,19 +2872,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1988-06-01</t>
+          <t>1988-02-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1988-06</t>
+          <t>1988-02</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2971,7 +2986,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +2994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3091,19 +3111,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1988-07-01</t>
+          <t>1988-03-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1988-07</t>
+          <t>1988-03</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3127,7 +3147,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3247,19 +3272,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1988-07-01</t>
+          <t>1988-03-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1988-07</t>
+          <t>1988-03</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3361,7 +3386,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3481,12 +3511,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1988-08-01</t>
+          <t>1988-04-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1988-08</t>
+          <t>1988-04</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3517,7 +3547,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3637,12 +3672,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1988-08-01</t>
+          <t>1988-04-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1988-08</t>
+          <t>1988-04</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3751,7 +3786,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3871,19 +3911,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1988-09-01</t>
+          <t>1988-05-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1988-09</t>
+          <t>1988-05</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3907,7 +3947,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3955,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4027,19 +4072,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1988-09-01</t>
+          <t>1988-05-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1988-09</t>
+          <t>1988-05</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4141,7 +4186,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4194,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4261,61 +4311,66 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1988-10-01</t>
+          <t>1988-06-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1988-10</t>
+          <t>1988-06</t>
         </is>
       </c>
       <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
         <v>2</v>
       </c>
-      <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT20" t="n">
-        <v>1</v>
-      </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4417,19 +4472,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1988-10-01</t>
+          <t>1988-06-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1988-10</t>
+          <t>1988-06</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4531,7 +4586,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4651,19 +4711,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1988-11-01</t>
+          <t>1988-07-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1988-11</t>
+          <t>1988-07</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4687,7 +4747,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4807,19 +4872,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1988-11-01</t>
+          <t>1988-07-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1988-11</t>
+          <t>1988-07</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -4921,7 +4986,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +4994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5041,61 +5111,66 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1988-12-01</t>
+          <t>1988-08-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1988-12</t>
+          <t>1988-08</t>
         </is>
       </c>
       <c r="N24" t="n">
+        <v>17</v>
+      </c>
+      <c r="O24" t="n">
+        <v>17</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="n">
-        <v>2</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT24" t="n">
-        <v>1</v>
-      </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5197,19 +5272,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1988-12-01</t>
+          <t>1988-08-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1988-12</t>
+          <t>1988-08</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5311,7 +5386,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5431,19 +5511,19 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1988-09-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1989-01</t>
+          <t>1988-09</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5467,7 +5547,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5587,19 +5672,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1988-09-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1989-01</t>
+          <t>1988-09</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5701,7 +5786,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5821,12 +5911,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1989-02-01</t>
+          <t>1988-10-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1989-02</t>
+          <t>1988-10</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5857,7 +5947,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5865,17 +5955,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5977,12 +6072,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1989-02-01</t>
+          <t>1988-10-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1989-02</t>
+          <t>1988-10</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -6091,7 +6186,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6099,17 +6194,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6211,12 +6311,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1989-03-01</t>
+          <t>1988-11-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1989-03</t>
+          <t>1988-11</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -6247,7 +6347,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6255,17 +6355,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6367,12 +6472,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1989-03-01</t>
+          <t>1988-11-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1989-03</t>
+          <t>1988-11</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -6481,7 +6586,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6489,17 +6594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6601,12 +6711,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1989-04-01</t>
+          <t>1988-12-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1989-04</t>
+          <t>1988-12</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -6637,7 +6747,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6757,12 +6872,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1989-04-01</t>
+          <t>1988-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1989-04</t>
+          <t>1988-12</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -6871,7 +6986,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +6994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6961,12 +7081,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6991,19 +7111,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1989-05-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1989-05</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>21523</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>21523</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7012,12 +7132,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -7037,7 +7157,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -7050,42 +7170,42 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7117,12 +7237,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7147,38 +7267,38 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1989-05-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1989-05</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>21523</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>21523</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Meslinger</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -7188,12 +7308,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -7203,7 +7323,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -7238,17 +7358,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7271,7 +7391,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D70_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -7284,42 +7404,42 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7501,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1989-06-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1989-06</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7417,7 +7537,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7545,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7537,12 +7662,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1989-06-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1989-06</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7651,7 +7776,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7784,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7771,12 +7901,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1989-07-01</t>
+          <t>1989-02-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1989-07</t>
+          <t>1989-02</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -7807,7 +7937,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7945,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7927,12 +8062,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1989-07-01</t>
+          <t>1989-02-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1989-07</t>
+          <t>1989-02</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -8041,7 +8176,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8184,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8161,12 +8301,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1989-08-01</t>
+          <t>1989-03-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1989-08</t>
+          <t>1989-03</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -8197,7 +8337,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8317,12 +8462,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1989-08-01</t>
+          <t>1989-03-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1989-08</t>
+          <t>1989-03</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -8431,7 +8576,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8551,19 +8701,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1989-09-01</t>
+          <t>1989-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1989-09</t>
+          <t>1989-04</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8587,7 +8737,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8707,19 +8862,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1989-09-01</t>
+          <t>1989-04-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1989-09</t>
+          <t>1989-04</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -8821,7 +8976,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +8984,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8941,61 +9101,66 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1989-10-01</t>
+          <t>1989-05-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1989-10</t>
+          <t>1989-05</t>
         </is>
       </c>
       <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
         <v>2</v>
       </c>
-      <c r="O44" t="n">
-        <v>2</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP44" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT44" t="n">
-        <v>1</v>
-      </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9097,19 +9262,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1989-10-01</t>
+          <t>1989-05-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1989-10</t>
+          <t>1989-05</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9211,7 +9376,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9384,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9331,19 +9501,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1989-11-01</t>
+          <t>1989-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1989-11</t>
+          <t>1989-06</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9367,7 +9537,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9545,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9487,19 +9662,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1989-11-01</t>
+          <t>1989-06-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1989-11</t>
+          <t>1989-06</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9601,7 +9776,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9784,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9721,19 +9901,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1989-12-01</t>
+          <t>1989-07-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1989-12</t>
+          <t>1989-07</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9757,7 +9937,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9945,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9877,19 +10062,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1989-12-01</t>
+          <t>1989-07-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1989-12</t>
+          <t>1989-07</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9991,7 +10176,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,55 +10184,2060 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1989-08-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1989-08</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
         <v>1</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV49" t="inlineStr">
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW49" t="inlineStr">
+      <c r="AW50" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr">
+      <c r="AY50" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA49" t="inlineStr">
+      <c r="BA50" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB49" t="inlineStr">
+      <c r="BB50" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1989-08-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1989-08</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1989-09-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1989-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1989-09-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1989-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1989-10-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1989-10</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1989-10-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1989-10</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1989-11-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1989-11</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1989-11-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1989-11</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1989-12-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1989-12</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1989-12-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>1989-12</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -10098,7 +12288,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
     </row>
@@ -10169,7 +12359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -10179,7 +12369,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -10199,7 +12389,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -10209,7 +12399,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -10231,7 +12421,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>146</v>
+        <v>44139</v>
       </c>
     </row>
     <row r="16">
